--- a/DATA_DIPA/DIPA_2024.xlsx
+++ b/DATA_DIPA/DIPA_2024.xlsx
@@ -519,7 +519,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E2" t="n">
         <v>9643323000</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         <v>2024</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E3" t="n">
         <v>8993615000</v>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         <v>2024</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E4" t="n">
         <v>8427963000</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>2024</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E6" t="n">
         <v>532922000</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>2024</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E10" t="n">
         <v>3455540000</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>2024</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E11" t="n">
         <v>9442749000</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>2024</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E13" t="n">
         <v>123000000</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>2024</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E15" t="n">
         <v>81500000</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>2024</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E16" t="n">
         <v>6503379000</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>2024</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E17" t="n">
         <v>7176810000</v>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>2024</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E19" t="n">
         <v>7696973000</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>2024</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E21" t="n">
         <v>2197343000</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>2024</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E22" t="n">
         <v>997036000</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>2024</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E23" t="n">
         <v>219666000</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>2024</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E24" t="n">
         <v>136401000</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>2024</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E26" t="n">
         <v>615600000</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>2024</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E28" t="n">
         <v>1389308000</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>2024</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E30" t="n">
         <v>946782000</v>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>2024</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E31" t="n">
         <v>2081212000</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>2024</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E33" t="n">
         <v>6536314000</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>2024</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E34" t="n">
         <v>42111399000</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>2024</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E35" t="n">
         <v>2816383000</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>2024</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E36" t="n">
         <v>1121516000</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>2024</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E37" t="n">
         <v>32800000</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>2024</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E39" t="n">
         <v>159985000</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>2024</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E40" t="n">
         <v>2829631141000</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>2024</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E41" t="n">
         <v>3387073000</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>2024</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E43" t="n">
         <v>932770000</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>2024</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E44" t="n">
         <v>790178000</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>2024</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E46" t="n">
         <v>437830000</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>2024</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E48" t="n">
         <v>2559541000</v>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>2024</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E49" t="n">
         <v>79797831000</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>2024</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E50" t="n">
         <v>1644258000</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>2024</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E51" t="n">
         <v>66475462000</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>2024</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E52" t="n">
         <v>89798549000</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>2024</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E53" t="n">
         <v>74173110000</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>2024</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E54" t="n">
         <v>561598000</v>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>2024</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E55" t="n">
         <v>1208242000</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>2024</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E58" t="n">
         <v>70797922000</v>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>2024</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E59" t="n">
         <v>3654338000</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>2024</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E60" t="n">
         <v>1591231000</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>2024</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E61" t="n">
         <v>299672000</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>2024</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E62" t="n">
         <v>168160000</v>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>2024</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E64" t="n">
         <v>5308929000</v>
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E65" t="n">
         <v>6661078000</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>2024</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E66" t="n">
         <v>5783920000</v>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>2024</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E67" t="n">
         <v>4497608000</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>2024</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E68" t="n">
         <v>46612188000</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>2024</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E69" t="n">
         <v>24214900000</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>2024</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E70" t="n">
         <v>13513308000</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>2024</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="E71" t="n">
         <v>632252318000</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>45657</v>
+        <v>46387</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
